--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104637_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104637_W20.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.238</v>
+        <v>6.1144</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6877</v>
+        <v>2.2779</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5503</v>
+        <v>3.8365</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0934</v>
+        <v>3.2002</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7099</v>
+        <v>1.6426</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3834</v>
+        <v>1.5576</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5209</v>
+        <v>2.0507</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8443</v>
+        <v>1.4856</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6765</v>
+        <v>0.5651</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4275</v>
+        <v>1.1495</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1344</v>
+        <v>0.157</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2931</v>
+        <v>0.9925</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>2.7316</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2373</v>
+        <v>0.3404</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6866</v>
+        <v>0.2271</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5507</v>
+        <v>0.1132</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0798</v>
+        <v>5.1641</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0604</v>
+        <v>4.6124</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0194</v>
+        <v>0.5517</v>
       </c>
       <c r="G3" t="n">
-        <v>3.209</v>
+        <v>4.0912</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6391</v>
+        <v>2.7057</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5699</v>
+        <v>1.3854</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0857</v>
+        <v>5.4946</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4995</v>
+        <v>3.8266</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5862000000000001</v>
+        <v>1.668</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1233</v>
+        <v>-1.4034</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1397</v>
+        <v>-1.1209</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9837</v>
+        <v>-0.2826</v>
       </c>
       <c r="P3" t="n">
-        <v>2.722</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.722</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6905</v>
+        <v>1.1624</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0253</v>
+        <v>0.6429</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3348</v>
+        <v>0.5195</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8685</v>
+        <v>4.1359</v>
       </c>
       <c r="E4" t="n">
-        <v>2.142</v>
+        <v>2.5969</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7264</v>
+        <v>1.539</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7825</v>
+        <v>3.7888</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5568</v>
+        <v>1.5648</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2257</v>
+        <v>2.2239</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4455</v>
+        <v>3.4289</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M4" t="n">
-        <v>0.337</v>
+        <v>0.3598</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1824</v>
+        <v>0.0708</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1693</v>
+        <v>0.3061</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.013</v>
+        <v>-0.2353</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>M. PANTZAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6911</v>
+        <v>0.696</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7018</v>
+        <v>-1.3656</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9893</v>
+        <v>2.0616</v>
       </c>
       <c r="G5" t="n">
-        <v>2.494</v>
+        <v>0.1342</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9320000000000001</v>
+        <v>-4.3419</v>
       </c>
       <c r="I5" t="n">
-        <v>1.562</v>
+        <v>4.4761</v>
       </c>
       <c r="J5" t="n">
-        <v>1.358</v>
+        <v>0.0033</v>
       </c>
       <c r="K5" t="n">
-        <v>0.052</v>
+        <v>-4.0107</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3061</v>
+        <v>4.0139</v>
       </c>
       <c r="M5" t="n">
-        <v>1.136</v>
+        <v>0.131</v>
       </c>
       <c r="N5" t="n">
-        <v>0.88</v>
+        <v>-0.3312</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2559</v>
+        <v>0.4622</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.722</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>3.0117</v>
+        <v>1.2659</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7462</v>
+        <v>0.7497</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2655</v>
+        <v>0.5162</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>-0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. PANTZAR</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.604</v>
+        <v>0.23</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7965</v>
+        <v>-0.8404</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4005</v>
+        <v>1.0704</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1521</v>
+        <v>2.5042</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.3287</v>
+        <v>0.9415</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4807</v>
+        <v>1.5626</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0469</v>
+        <v>1.355</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.9806</v>
+        <v>0.0517</v>
       </c>
       <c r="L6" t="n">
-        <v>4.0275</v>
+        <v>1.3033</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1052</v>
+        <v>1.1492</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.348</v>
+        <v>0.8898</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4532</v>
+        <v>0.2593</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4952</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>2.157</v>
+        <v>1.5469</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2642</v>
+        <v>1.2191</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8928</v>
+        <v>0.3278</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>M. NORMANTAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6876</v>
+        <v>-2.43</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8898</v>
+        <v>-1.4061</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7978</v>
+        <v>-1.0239</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4036</v>
+        <v>-1.7852</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4326</v>
+        <v>-1.9072</v>
       </c>
       <c r="I7" t="n">
-        <v>1.029</v>
+        <v>0.122</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0447</v>
+        <v>-0.5253</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5897</v>
+        <v>-0.614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6344</v>
+        <v>0.0887</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4484</v>
+        <v>-1.2599</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8429</v>
+        <v>-1.2932</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3946</v>
+        <v>0.0333</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0356</v>
+        <v>-0.0106</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3338</v>
+        <v>0.2574</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2982</v>
+        <v>-0.268</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. NORMANTAS</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1964</v>
+        <v>-2.9245</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7331</v>
+        <v>-2.0376</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4633</v>
+        <v>-0.8869</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7853</v>
+        <v>-1.4076</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9105</v>
+        <v>-2.4463</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1253</v>
+        <v>1.0387</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4991</v>
+        <v>0.0115</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.603</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1038</v>
+        <v>0.633</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2861</v>
+        <v>-1.4191</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3075</v>
+        <v>-1.8248</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0214</v>
+        <v>0.4057</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7721</v>
+        <v>-0.1998</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0998</v>
+        <v>0.2271</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6723</v>
+        <v>-0.427</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0985</v>
+        <v>-3.2445</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3522</v>
+        <v>-2.4909</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7463</v>
+        <v>-0.7536</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1522</v>
+        <v>-3.162</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7848</v>
+        <v>-1.7945</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3674</v>
+        <v>-1.3675</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6102</v>
+        <v>-1.6427</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6345</v>
+        <v>-0.6592</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9756</v>
+        <v>-0.9835</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.542</v>
+        <v>-1.5193</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7195</v>
+        <v>0.1451</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6079</v>
+        <v>0.29</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1116</v>
+        <v>-0.1449</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8089</v>
+        <v>-5.9215</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.3659</v>
+        <v>-8.8103</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5571</v>
+        <v>2.8889</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9659</v>
+        <v>-3.9749</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7561</v>
+        <v>-1.7549</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2098</v>
+        <v>-2.22</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.286</v>
+        <v>-5.3096</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2898</v>
+        <v>-2.3</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.9962</v>
+        <v>-3.0096</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3201</v>
+        <v>1.3347</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2551</v>
+        <v>-0.3531</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6775</v>
+        <v>-0.0863</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5777</v>
+        <v>-0.2669</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.0527</v>
+        <v>-12.8505</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.8756</v>
+        <v>-10.9168</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1771</v>
+        <v>-1.9337</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.2081</v>
+        <v>-7.2131</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.3</v>
+        <v>-4.3023</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.9081</v>
+        <v>-2.9108</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.3833</v>
+        <v>-5.4068</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.0242</v>
+        <v>-3.0379</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.3591</v>
+        <v>-2.3689</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8248</v>
+        <v>-1.8062</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.9903</v>
+        <v>-5.0079</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1473</v>
+        <v>0.073</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1785</v>
+        <v>0.1808</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3257</v>
+        <v>-0.1078</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.3627</v>
+        <v>-11.0306</v>
       </c>
       <c r="E12" t="n">
-        <v>-18.4212</v>
+        <v>-18.3805</v>
       </c>
       <c r="F12" t="n">
-        <v>7.0585</v>
+        <v>7.35</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.784099999999999</v>
+        <v>-3.824199999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.674900000000001</v>
+        <v>-9.692499999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>5.8907</v>
+        <v>5.867999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2768999999999995</v>
+        <v>-0.5404000000000009</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.9943</v>
+        <v>-4.1557</v>
       </c>
       <c r="L12" t="n">
-        <v>3.717500000000001</v>
+        <v>3.615199999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.5072</v>
+        <v>-3.283700000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.680400000000001</v>
+        <v>-5.5366</v>
       </c>
       <c r="O12" t="n">
-        <v>2.1731</v>
+        <v>2.2528</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.5365</v>
+        <v>-4.5525</v>
       </c>
       <c r="Q12" t="n">
-        <v>-21.5492</v>
+        <v>-21.6252</v>
       </c>
       <c r="R12" t="n">
-        <v>17.0125</v>
+        <v>17.0723</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6747</v>
+        <v>4.041</v>
       </c>
       <c r="T12" t="n">
-        <v>3.6295</v>
+        <v>4.0139</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0452999999999999</v>
+        <v>0.02679999999999993</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.7169</v>
+        <v>-6.694699999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.492</v>
+        <v>-6.465599999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.2202</v>
+        <v>9.055300000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>6.8224</v>
+        <v>6.4372</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3978</v>
+        <v>2.6181</v>
       </c>
       <c r="G13" t="n">
-        <v>5.2555</v>
+        <v>5.2678</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4717</v>
+        <v>4.4718</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.796</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9189</v>
+        <v>3.9011</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8443</v>
+        <v>3.8266</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3365</v>
+        <v>1.3668</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7091</v>
+        <v>0.7215</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1546</v>
+        <v>-0.3216</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5989</v>
+        <v>0.2481</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7534</v>
+        <v>-0.5697</v>
       </c>
       <c r="V13" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="W13" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4729</v>
+        <v>7.1808</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4165</v>
+        <v>4.144</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0564</v>
+        <v>3.0368</v>
       </c>
       <c r="G14" t="n">
-        <v>5.1517</v>
+        <v>5.1574</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7069</v>
+        <v>3.7078</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4448</v>
+        <v>1.4496</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7665</v>
+        <v>4.7366</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1272</v>
+        <v>3.1059</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3852</v>
+        <v>0.4208</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5797</v>
+        <v>0.6019</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7748</v>
+        <v>0.4787</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8257</v>
+        <v>0.5942</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0508</v>
+        <v>-0.1155</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3166</v>
+        <v>4.8392</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3593</v>
+        <v>1.6198</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9573</v>
+        <v>3.2194</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3059</v>
+        <v>1.311</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8657</v>
+        <v>1.8695</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5598</v>
+        <v>-0.5586</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0352</v>
+        <v>1.006</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3019</v>
+        <v>1.282</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2707</v>
+        <v>0.3049</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5638</v>
+        <v>0.5875</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1279</v>
+        <v>-0.3611</v>
       </c>
       <c r="T15" t="n">
-        <v>0.617</v>
+        <v>-0.0887</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4891</v>
+        <v>-0.2724</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0404</v>
+        <v>0.7401</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8243</v>
+        <v>-2.8486</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7839</v>
+        <v>3.5886</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.983</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1327</v>
+        <v>-0.3047</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8502999999999999</v>
+        <v>0.3956</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.6351</v>
+        <v>-0.2281</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.5074</v>
+        <v>-1.1656</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1276</v>
+        <v>0.9375</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6521</v>
+        <v>0.319</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3748</v>
+        <v>0.8609</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2773</v>
+        <v>-0.5419</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.806</v>
+        <v>-0.2614</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3085</v>
+        <v>-0.3441</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4976</v>
+        <v>0.0827</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1002</v>
+        <v>0.517</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.2826</v>
+        <v>-1.3534</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1824</v>
+        <v>1.8704</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1015</v>
+        <v>1.5087</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3089</v>
+        <v>-0.5623</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4104</v>
+        <v>2.071</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1977</v>
+        <v>1.1184</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1571</v>
+        <v>-0.0732</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9594</v>
+        <v>1.1916</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2992</v>
+        <v>0.3903</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8483000000000001</v>
+        <v>-0.4891</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.549</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1757</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1091</v>
+        <v>-0.5364</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8166</v>
+        <v>-0.1955</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2925</v>
+        <v>-0.341</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3735</v>
+        <v>0.4733</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0242</v>
+        <v>-2.5178</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6507</v>
+        <v>2.9912</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5095</v>
+        <v>-1.9818</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.551</v>
+        <v>-1.1344</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0605</v>
+        <v>-0.8475</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1484</v>
+        <v>-2.6752</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0457</v>
+        <v>-1.5351</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1941</v>
+        <v>-1.1401</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3611</v>
+        <v>0.6933</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5053</v>
+        <v>0.4007</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.2926</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>3.1868</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4294</v>
+        <v>-0.296</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9043</v>
+        <v>0.0483</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5251</v>
+        <v>-0.3442</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7784</v>
+        <v>-1.2092</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6399</v>
+        <v>-2.1248</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.9156</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4068</v>
+        <v>-2.4011</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3867</v>
+        <v>0.3904</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7935</v>
+        <v>-2.7915</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.661</v>
+        <v>-1.6739</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.163</v>
+        <v>-0.1691</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7458</v>
+        <v>-0.7271</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5496</v>
+        <v>0.5595</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2427</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1553</v>
+        <v>0.6873</v>
       </c>
       <c r="U19" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.1176</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="20">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7754</v>
+        <v>-1.7765</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8559</v>
+        <v>-0.8593</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9195</v>
+        <v>-0.9171</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3913</v>
+        <v>-1.3909</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5327</v>
+        <v>-1.5344</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.605</v>
+        <v>-0.6012</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3841</v>
+        <v>-0.3856</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3145</v>
+        <v>-0.3159</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0261</v>
+        <v>-1.9567</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.9526</v>
+        <v>-5.5171</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9265</v>
+        <v>3.5604</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2169</v>
+        <v>1.2291</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7256</v>
+        <v>2.7365</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5087</v>
+        <v>-1.5074</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7836</v>
+        <v>1.7754</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3343</v>
+        <v>0.3627</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9419</v>
+        <v>0.9611</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R21" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9747</v>
+        <v>-0.9094</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1644</v>
+        <v>-0.6926</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8103</v>
+        <v>-0.2168</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5527</v>
+        <v>-4.905</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0772</v>
+        <v>-4.3301</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4755</v>
+        <v>-0.575</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.9758</v>
+        <v>-4.9669</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6306</v>
+        <v>-1.6259</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3452</v>
+        <v>-3.341</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.9642</v>
+        <v>-2.9779</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5034</v>
+        <v>-1.5103</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0116</v>
+        <v>-1.989</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0375</v>
+        <v>-0.3251</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0212</v>
+        <v>-0.214</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0163</v>
+        <v>-0.1111</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>11.363</v>
+        <v>12.9583</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.0585</v>
+        <v>-7.3501</v>
       </c>
       <c r="F23" t="n">
-        <v>18.4214</v>
+        <v>20.3084</v>
       </c>
       <c r="G23" t="n">
-        <v>3.7841</v>
+        <v>3.8242</v>
       </c>
       <c r="H23" t="n">
-        <v>9.674800000000001</v>
+        <v>9.6922</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.8907</v>
+        <v>-5.8682</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5072</v>
+        <v>3.283800000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>5.680400000000001</v>
+        <v>5.5366</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.1732</v>
+        <v>-2.2527</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2766999999999995</v>
+        <v>0.5405000000000004</v>
       </c>
       <c r="N23" t="n">
-        <v>3.994400000000001</v>
+        <v>4.1557</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.7176</v>
+        <v>-3.6151</v>
       </c>
       <c r="P23" t="n">
-        <v>4.5367</v>
+        <v>4.5526</v>
       </c>
       <c r="Q23" t="n">
-        <v>-17.0125</v>
+        <v>-17.0725</v>
       </c>
       <c r="R23" t="n">
-        <v>21.5494</v>
+        <v>21.6251</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.675</v>
+        <v>-2.113</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.04530000000000001</v>
+        <v>-0.02670000000000008</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.629599999999999</v>
+        <v>-2.0863</v>
       </c>
       <c r="V23" t="n">
-        <v>6.7168</v>
+        <v>6.694699999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>6.491899999999999</v>
+        <v>6.4654</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2249</v>
+        <v>0.2293000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104637_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104637_W20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-6.465599999999999</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104637_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>0.2293000000000001</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
